--- a/DOSSIES_MULTIFORMATO/SEMIG/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SEMIG/dossie.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>235353.15</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -756,14 +756,10 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025NE0000009</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3/2024</t>
-        </is>
-      </c>
+          <t>2025NE0000010</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>22/01/2025</t>
@@ -779,17 +775,21 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CT - Prestação de Serviços de Tecnologia da Informação e Comunicação (TIC) para atender às necessidades da Secretaria de Estado - SEMIG.</t>
+          <t>Anulação para atualização de ndata de emissão de NE.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025NE0000010</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>2025NE0000009</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3/2024</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>22/01/2025</t>
@@ -805,7 +805,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anulação para atualização de ndata de emissão de NE.</t>
+          <t>CT - Prestação de Serviços de Tecnologia da Informação e Comunicação (TIC) para atender às necessidades da Secretaria de Estado - SEMIG.</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025NE0000075</t>
+          <t>2025NE0000076</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>98290.55</v>
+        <v>314.58</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025NE0000076</t>
+          <t>2025NE0000075</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>314.58</v>
+        <v>98290.55</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024NE0000276</t>
+          <t>2024NE0000277</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>67702.72</v>
+        <v>259932.38</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024NE0000277</t>
+          <t>2024NE0000276</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>259932.38</v>
+        <v>67702.72</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024NE0000056</t>
+          <t>2024NE00057</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>32763.51</v>
+        <v>314.57</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1045,14 +1045,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CT - Prestação de Serviços de Tecnologia da Informação e Comunicação (TIC) para atender às necessidades da Secretaria de Estado - SEMIG.</t>
+          <t>Serviço em TI</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024NE0000057</t>
+          <t>2024NE00056</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>314.57</v>
+        <v>32763.51</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1075,14 +1075,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CT - Prestação de Serviços de Tecnologia da Informação e Comunicação (TIC) para atender às necessidades da Secretaria de Estado - SEMIG.</t>
+          <t>Serviço em TI</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024NE00056</t>
+          <t>2024NE0000057</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>32763.51</v>
+        <v>314.57</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1105,14 +1105,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Serviço em TI</t>
+          <t>CT - Prestação de Serviços de Tecnologia da Informação e Comunicação (TIC) para atender às necessidades da Secretaria de Estado - SEMIG.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024NE00057</t>
+          <t>2024NE0000056</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>314.57</v>
+        <v>32763.51</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Serviço em TI</t>
+          <t>CT - Prestação de Serviços de Tecnologia da Informação e Comunicação (TIC) para atender às necessidades da Secretaria de Estado - SEMIG.</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025NE0000011</t>
+          <t>2025NE0000013</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>629.14</v>
+        <v>131054.04</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025NE0000013</t>
+          <t>2025NE0000011</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>131054.04</v>
+        <v>629.14</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>

--- a/DOSSIES_MULTIFORMATO/SEMIG/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SEMIG/dossie.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2029-06-30</t>
         </is>
       </c>
     </row>
